--- a/outputs/master_rename_build/tables/build_comparison.xlsx
+++ b/outputs/master_rename_build/tables/build_comparison.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="18" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="19" uniqueCount="13">
   <si>
     <t>Metric</t>
   </si>
@@ -48,7 +48,10 @@
     <t>unit variable: harmonized_nsu_unit (new) vs cleaned_nsu_unit (pre-Aug11)</t>
   </si>
   <si>
-    <t>the new build drops nothing for being MS-only or standard-unit-looking; see cleaning_Aug11.do header note 3</t>
+    <t>MS-only rows are no longer dropped (master has 0 of them); standard-quantity labels ARE still dropped -- 10 labels / 33 weighings, listed in excluded_standard_unit_obs.xlsx</t>
+  </si>
+  <si>
+    <t>see cleaning_Aug11.do header note 3 for why those two old filters are separate exclusions</t>
   </si>
 </sst>
 </file>
@@ -172,7 +175,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -191,7 +194,7 @@
         <v>3</v>
       </c>
       <c r="B2">
-        <v>11491</v>
+        <v>11458</v>
       </c>
       <c r="C2">
         <v>11259</v>
@@ -213,7 +216,7 @@
         <v>5</v>
       </c>
       <c r="B4">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="C4">
         <v>65</v>
@@ -224,7 +227,7 @@
         <v>6</v>
       </c>
       <c r="B5">
-        <v>102</v>
+        <v>93</v>
       </c>
       <c r="C5">
         <v>102</v>
@@ -235,7 +238,7 @@
         <v>7</v>
       </c>
       <c r="B6">
-        <v>1961</v>
+        <v>1952</v>
       </c>
       <c r="C6">
         <v>1917</v>
@@ -246,7 +249,7 @@
         <v>8</v>
       </c>
       <c r="B7">
-        <v>230</v>
+        <v>221</v>
       </c>
       <c r="C7">
         <v>231</v>
@@ -267,6 +270,11 @@
         <v>11</v>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>12</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/outputs/master_rename_build/tables/build_comparison.xlsx
+++ b/outputs/master_rename_build/tables/build_comparison.xlsx
@@ -48,7 +48,7 @@
     <t>unit variable: harmonized_nsu_unit (new) vs cleaned_nsu_unit (pre-Aug11)</t>
   </si>
   <si>
-    <t>MS-only rows are no longer dropped (master has 0 of them); standard-quantity labels ARE still dropped -- 10 labels / 33 weighings, listed in excluded_standard_unit_obs.xlsx</t>
+    <t>MS-only rows are no longer dropped (master has 0 of them); non-NSU labels ARE still dropped -- 10 labels / 38 weighings (standard quantity, ambiguous quantity, not a unit), listed in excluded_standard_unit_obs.xlsx</t>
   </si>
   <si>
     <t>see cleaning_Aug11.do header note 3 for why those two old filters are separate exclusions</t>
@@ -194,7 +194,7 @@
         <v>3</v>
       </c>
       <c r="B2">
-        <v>11458</v>
+        <v>11453</v>
       </c>
       <c r="C2">
         <v>11259</v>
@@ -216,7 +216,7 @@
         <v>5</v>
       </c>
       <c r="B4">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C4">
         <v>65</v>
@@ -227,7 +227,7 @@
         <v>6</v>
       </c>
       <c r="B5">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C5">
         <v>102</v>
@@ -238,7 +238,7 @@
         <v>7</v>
       </c>
       <c r="B6">
-        <v>1952</v>
+        <v>1951</v>
       </c>
       <c r="C6">
         <v>1917</v>
@@ -249,7 +249,7 @@
         <v>8</v>
       </c>
       <c r="B7">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C7">
         <v>231</v>

--- a/outputs/master_rename_build/tables/build_comparison.xlsx
+++ b/outputs/master_rename_build/tables/build_comparison.xlsx
@@ -51,7 +51,7 @@
     <t>MS-only rows are no longer dropped (master has 0 of them); non-NSU labels ARE still dropped -- 10 labels / 38 weighings (standard quantity, ambiguous quantity, not a unit), listed in excluded_standard_unit_obs.xlsx</t>
   </si>
   <si>
-    <t>see cleaning_Aug11.do header note 3 for why those two old filters are separate exclusions</t>
+    <t>see 03_clean_ms.do header note 3 for why those two old filters are separate exclusions</t>
   </si>
 </sst>
 </file>

--- a/outputs/master_rename_build/tables/build_comparison.xlsx
+++ b/outputs/master_rename_build/tables/build_comparison.xlsx
@@ -48,7 +48,7 @@
     <t>unit variable: harmonized_nsu_unit (new) vs cleaned_nsu_unit (pre-Aug11)</t>
   </si>
   <si>
-    <t>MS-only rows are no longer dropped (master has 0 of them); non-NSU labels ARE still dropped -- 10 labels / 38 weighings (standard quantity, ambiguous quantity, not a unit), listed in excluded_standard_unit_obs.xlsx</t>
+    <t>MS-only rows are no longer dropped (master has 0 of them); non-NSU labels ARE still dropped -- 11 labels / 42 weighings (standard quantity, ambiguous quantity, not a unit), listed in excluded_standard_unit_obs.xlsx</t>
   </si>
   <si>
     <t>see 03_clean_ms.do header note 3 for why those two old filters are separate exclusions</t>
@@ -194,7 +194,7 @@
         <v>3</v>
       </c>
       <c r="B2">
-        <v>11453</v>
+        <v>11449</v>
       </c>
       <c r="C2">
         <v>11259</v>
@@ -216,7 +216,7 @@
         <v>5</v>
       </c>
       <c r="B4">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C4">
         <v>65</v>
@@ -227,7 +227,7 @@
         <v>6</v>
       </c>
       <c r="B5">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C5">
         <v>102</v>
@@ -238,7 +238,7 @@
         <v>7</v>
       </c>
       <c r="B6">
-        <v>1951</v>
+        <v>1949</v>
       </c>
       <c r="C6">
         <v>1917</v>
@@ -249,7 +249,7 @@
         <v>8</v>
       </c>
       <c r="B7">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C7">
         <v>231</v>

--- a/outputs/master_rename_build/tables/build_comparison.xlsx
+++ b/outputs/master_rename_build/tables/build_comparison.xlsx
@@ -238,7 +238,7 @@
         <v>7</v>
       </c>
       <c r="B6">
-        <v>1949</v>
+        <v>1948</v>
       </c>
       <c r="C6">
         <v>1917</v>

--- a/outputs/master_rename_build/tables/build_comparison.xlsx
+++ b/outputs/master_rename_build/tables/build_comparison.xlsx
@@ -48,7 +48,7 @@
     <t>unit variable: harmonized_nsu_unit (new) vs cleaned_nsu_unit (pre-Aug11)</t>
   </si>
   <si>
-    <t>MS-only rows are no longer dropped (master has 0 of them); non-NSU labels ARE still dropped -- 11 labels / 42 weighings (standard quantity, ambiguous quantity, not a unit), listed in excluded_standard_unit_obs.xlsx</t>
+    <t>MS-only rows are no longer dropped (master has 0 of them); non-NSU labels ARE still dropped -- 16 labels / 58 weighings (standard quantity, ambiguous quantity, not a unit), listed in excluded_standard_unit_obs.xlsx</t>
   </si>
   <si>
     <t>see 03_clean_ms.do header note 3 for why those two old filters are separate exclusions</t>
@@ -194,7 +194,7 @@
         <v>3</v>
       </c>
       <c r="B2">
-        <v>11449</v>
+        <v>11433</v>
       </c>
       <c r="C2">
         <v>11259</v>
@@ -216,7 +216,7 @@
         <v>5</v>
       </c>
       <c r="B4">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="C4">
         <v>65</v>
@@ -227,7 +227,7 @@
         <v>6</v>
       </c>
       <c r="B5">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="C5">
         <v>102</v>
@@ -238,7 +238,7 @@
         <v>7</v>
       </c>
       <c r="B6">
-        <v>1948</v>
+        <v>1943</v>
       </c>
       <c r="C6">
         <v>1917</v>
@@ -249,7 +249,7 @@
         <v>8</v>
       </c>
       <c r="B7">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="C7">
         <v>231</v>
